--- a/experiment/result.xlsx
+++ b/experiment/result.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ted\Desktop\論文\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{020A9B91-32D7-4252-961A-2E8BE10F632D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3407950-D6F6-40E8-8E87-824967C77651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4C5C6A26-9A3B-411A-9AB6-AE890C61EC84}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{4C5C6A26-9A3B-411A-9AB6-AE890C61EC84}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="164">
   <si>
     <t>門檻</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -496,6 +495,199 @@
   </si>
   <si>
     <t>eps=0.08,step=0.03,iter=13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shap Difference + EFIS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shap Difference+Threshold</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8960</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MLP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9997</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9950</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>eps=0.080,step=0.030,iter=20</t>
+  </si>
+  <si>
+    <t>0.9830</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9888</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9366</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9380</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">eps=0.080 </t>
+  </si>
+  <si>
+    <t>0.9390</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9996</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9817</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9820</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Method</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shap Signature Difference + MLP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shap Signature Difference + RF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9880</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9983</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9400</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>eps=0.080,step=0.030,iter=33</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8730</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9740</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9530</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9927</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9162</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9681</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9170</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9670</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mnist(fgsm,pgd)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cifar10(deepfool)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Train</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7370</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6517</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9719</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8820</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_iter=100, eps=0.008, nb_grads=5</t>
+  </si>
+  <si>
+    <t>Shap Signature Difference + EFIS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8180</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8444</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8195</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8210</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8448</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8437</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8680</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -503,7 +695,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -544,16 +736,39 @@
       <family val="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor theme="5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -576,13 +791,81 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="5"/>
+      </right>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="5"/>
+      </right>
+      <top style="thin">
+        <color theme="5"/>
+      </top>
+      <bottom style="thin">
+        <color theme="5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -595,16 +878,61 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -613,58 +941,28 @@
   </cellStyles>
   <dxfs count="64">
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <family val="1"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <family val="1"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <family val="1"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <family val="1"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
@@ -703,6 +1001,16 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <family val="1"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -738,6 +1046,16 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <family val="1"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -770,6 +1088,16 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <family val="1"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
@@ -1034,64 +1362,64 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{520FEA86-4C1C-49EF-AFE2-BC7FA57F1FF0}" name="表格2_7" displayName="表格2_7" ref="A36:G39" totalsRowShown="0" headerRowDxfId="31">
-  <autoFilter ref="A36:G39" xr:uid="{520FEA86-4C1C-49EF-AFE2-BC7FA57F1FF0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{520FEA86-4C1C-49EF-AFE2-BC7FA57F1FF0}" name="表格2_7" displayName="表格2_7" ref="A37:G40" totalsRowShown="0" headerRowDxfId="31">
+  <autoFilter ref="A37:G40" xr:uid="{520FEA86-4C1C-49EF-AFE2-BC7FA57F1FF0}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{55B0D1D6-2807-49C2-85E2-E541A31D52B6}" name="Attack               " dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{F3D1DEC5-F7E6-4664-87B1-BA23B39BD65C}" name=" Detection(accuracy)" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{6D55C80D-3C1C-4029-B2EE-490C50834607}" name="F1-Score" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{625B6D82-FA6D-4D61-9FFA-B654D2401E22}" name="AUC" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{724997A2-8E7A-4DBF-B15C-982C19B74C54}" name=" Rules" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{F0B86DD3-89FA-4388-87AB-17535A13C073}" name=" Success Rate" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{16AD339E-D562-49C9-AC21-26F430D01003}" name="Params" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{55B0D1D6-2807-49C2-85E2-E541A31D52B6}" name="Attack               " dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{F3D1DEC5-F7E6-4664-87B1-BA23B39BD65C}" name=" Detection(accuracy)" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{6D55C80D-3C1C-4029-B2EE-490C50834607}" name="F1-Score" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{625B6D82-FA6D-4D61-9FFA-B654D2401E22}" name="AUC" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{724997A2-8E7A-4DBF-B15C-982C19B74C54}" name=" Rules" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{F0B86DD3-89FA-4388-87AB-17535A13C073}" name=" Success Rate" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{16AD339E-D562-49C9-AC21-26F430D01003}" name="Params" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{567CD184-7F9B-44CA-91A8-D4CF0D2DA32B}" name="表格1_7109" displayName="表格1_7109" ref="A31:G34" totalsRowShown="0" headerRowDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{567CD184-7F9B-44CA-91A8-D4CF0D2DA32B}" name="表格1_7109" displayName="表格1_7109" ref="A31:G34" totalsRowShown="0" headerRowDxfId="23">
   <autoFilter ref="A31:G34" xr:uid="{567CD184-7F9B-44CA-91A8-D4CF0D2DA32B}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{99BC2345-904F-4395-A2FC-089190C89D20}" name="Attack               " dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{711228F0-53B4-417C-AC90-C5D6238901B9}" name=" Detection(accuracy)" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{E303FABF-81BB-4982-95E3-913C34F05904}" name="F1-Score" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{C55A2DC5-73CC-4AFC-A21D-BB208F14899F}" name="AUC" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{8FD73151-666F-4D46-8444-8A94BB8B875E}" name="Threshold" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{31AA62BB-0940-41C9-8A86-BB04FD4CE8DF}" name=" Success Rate" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{18532987-53D9-46D7-AE29-638C1EB51220}" name="Params" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{99BC2345-904F-4395-A2FC-089190C89D20}" name="Attack               " dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{711228F0-53B4-417C-AC90-C5D6238901B9}" name=" Detection(accuracy)" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{E303FABF-81BB-4982-95E3-913C34F05904}" name="F1-Score" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{C55A2DC5-73CC-4AFC-A21D-BB208F14899F}" name="AUC" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{8FD73151-666F-4D46-8444-8A94BB8B875E}" name="Threshold" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{31AA62BB-0940-41C9-8A86-BB04FD4CE8DF}" name=" Success Rate" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{18532987-53D9-46D7-AE29-638C1EB51220}" name="Params" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{0A7FF302-F1F1-4D39-B85D-B79E6B82691A}" name="表格2_710" displayName="表格2_710" ref="I36:O39" totalsRowShown="0" headerRowDxfId="19">
-  <autoFilter ref="I36:O39" xr:uid="{0A7FF302-F1F1-4D39-B85D-B79E6B82691A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{0A7FF302-F1F1-4D39-B85D-B79E6B82691A}" name="表格2_710" displayName="表格2_710" ref="I37:O40" totalsRowShown="0" headerRowDxfId="15">
+  <autoFilter ref="I37:O40" xr:uid="{0A7FF302-F1F1-4D39-B85D-B79E6B82691A}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{AAC304E8-5C13-4B6F-AE64-2EAC1EEF1E6C}" name="Attack               " dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{A86B16E2-29D5-4A14-B970-DFDC30F4842D}" name=" Detection(accuracy)" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{60114417-8DE9-4A8A-B999-F2AB726A3880}" name="F1-Score" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{FF390DCF-4A97-4107-9D5F-B84B134B2741}" name="AUC" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{E747C042-1772-40C2-8EC7-C6EF5107BC6E}" name=" Rules" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{DBE2051E-83F1-4C68-93B9-08F8BFFAD0FE}" name=" Success Rate" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{8F647F5B-1D09-4310-A23B-B20C661804C5}" name="Params" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{AAC304E8-5C13-4B6F-AE64-2EAC1EEF1E6C}" name="Attack               " dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{A86B16E2-29D5-4A14-B970-DFDC30F4842D}" name=" Detection(accuracy)" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{60114417-8DE9-4A8A-B999-F2AB726A3880}" name="F1-Score" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{FF390DCF-4A97-4107-9D5F-B84B134B2741}" name="AUC" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{E747C042-1772-40C2-8EC7-C6EF5107BC6E}" name=" Rules" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{DBE2051E-83F1-4C68-93B9-08F8BFFAD0FE}" name=" Success Rate" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{8F647F5B-1D09-4310-A23B-B20C661804C5}" name="Params" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{92B2A9D8-4BD1-473C-809F-B42412CFF1D5}" name="表格1_710911" displayName="表格1_710911" ref="I31:O34" totalsRowShown="0" headerRowDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{92B2A9D8-4BD1-473C-809F-B42412CFF1D5}" name="表格1_710911" displayName="表格1_710911" ref="I31:O34" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="I31:O34" xr:uid="{92B2A9D8-4BD1-473C-809F-B42412CFF1D5}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9423453E-B753-4863-A726-EF6E88584F09}" name="Attack               " dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{1123E40B-1965-4BD3-825B-EBB5D48CA1ED}" name=" Detection(accuracy)" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{F5A074FC-9D52-4B21-BE30-44FE71F2FB93}" name="F1-Score" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{ADD8F174-49F2-4C10-81A5-F6370802C539}" name="AUC" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{E8CAB221-A015-4128-9A89-002095C9D4BF}" name="Threshold" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{EC46B93F-1C93-49C5-837C-FECFB3AF8099}" name=" Success Rate" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{934E9612-351C-46D8-8F85-7FB91194BF17}" name="Params" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{9423453E-B753-4863-A726-EF6E88584F09}" name="Attack               " dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{1123E40B-1965-4BD3-825B-EBB5D48CA1ED}" name=" Detection(accuracy)" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{F5A074FC-9D52-4B21-BE30-44FE71F2FB93}" name="F1-Score" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{ADD8F174-49F2-4C10-81A5-F6370802C539}" name="AUC" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{E8CAB221-A015-4128-9A89-002095C9D4BF}" name="Threshold" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{EC46B93F-1C93-49C5-837C-FECFB3AF8099}" name=" Success Rate" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{934E9612-351C-46D8-8F85-7FB91194BF17}" name="Params" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1415,26 +1743,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B5CF606-6A0F-4330-BA1B-636FBD718E8F}">
   <dimension ref="A1:O108"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="34.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1448,7 +1778,7 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1464,7 +1794,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1480,7 +1810,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1490,19 +1820,19 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1512,7 +1842,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
@@ -1524,7 +1854,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -1547,7 +1877,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -1570,7 +1900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1579,7 +1909,7 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1589,7 +1919,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
@@ -1601,7 +1931,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
@@ -1624,7 +1954,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
@@ -1647,7 +1977,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1656,7 +1986,7 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1666,7 +1996,7 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>4</v>
       </c>
@@ -1678,7 +2008,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>9</v>
       </c>
@@ -1702,7 +2032,7 @@
       </c>
       <c r="H18" s="2"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
@@ -1726,7 +2056,7 @@
       </c>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1736,7 +2066,7 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -1748,7 +2078,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
@@ -1760,7 +2090,7 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>9</v>
       </c>
@@ -1788,7 +2118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>16</v>
       </c>
@@ -1812,7 +2142,7 @@
       </c>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -1822,7 +2152,12 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I30" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>9</v>
       </c>
@@ -1866,7 +2201,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>16</v>
       </c>
@@ -1910,7 +2245,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>23</v>
       </c>
@@ -1955,8 +2290,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -1977,7 +2312,7 @@
       <c r="G34" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="I34" s="4" t="s">
         <v>85</v>
       </c>
       <c r="J34" s="2" t="s">
@@ -1999,224 +2334,632 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="7"/>
-      <c r="I35" s="7"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="5"/>
+      <c r="I36" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B37" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F37" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G37" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I36" s="6" t="s">
+      <c r="I37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="J37" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="K37" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L36" s="3" t="s">
+      <c r="L37" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M36" s="3" t="s">
+      <c r="M37" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N36" s="3" t="s">
+      <c r="N37" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O36" s="3" t="s">
+      <c r="O37" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F38" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G38" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I38" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="J38" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="K38" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="L38" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="M38" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="N37" s="2" t="s">
+      <c r="N38" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="O37" s="2" t="s">
+      <c r="O38" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B39" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G39" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="H38" s="2"/>
-      <c r="I38" s="3" t="s">
+      <c r="H39" s="2"/>
+      <c r="I39" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J38" s="2" t="s">
+      <c r="J39" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="K38" s="2" t="s">
+      <c r="K39" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="L38" s="2" t="s">
+      <c r="L39" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="M39" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="N38" s="2" t="s">
+      <c r="N39" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="O38" s="2" t="s">
+      <c r="O39" s="2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B40" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G40" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="H39" s="2"/>
-      <c r="I39" s="6" t="s">
+      <c r="H40" s="2"/>
+      <c r="I40" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="J39" s="2" t="s">
+      <c r="J40" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K39" s="2" t="s">
+      <c r="K40" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="L39" s="2" t="s">
+      <c r="L40" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="M39" s="2" t="s">
+      <c r="M40" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="N39" s="2" t="s">
+      <c r="N40" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O39" s="2" t="s">
+      <c r="O40" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="7"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="H42" s="2"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="5"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="I42" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H43" s="2"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="I43" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J43" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="N43" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="O43" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H44" s="2"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="I44" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="K44" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="L44" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="M44" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="N44" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="O44" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H45" s="2"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="I45" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J45" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="K45" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="L45" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="M45" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="N45" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="O45" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H46" s="2"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="H47" s="2" t="s">
+      <c r="I46" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="K46" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="L46" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="M46" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="N46" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="O46" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="H47" s="2"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="H48" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="H48" s="2"/>
-    </row>
-    <row r="49" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="I48" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+    </row>
+    <row r="49" spans="8:15" x14ac:dyDescent="0.25">
       <c r="H49" s="2"/>
-    </row>
-    <row r="50" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="I49" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J49" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="N49" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="O49" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="8:15" x14ac:dyDescent="0.25">
       <c r="H50" s="2"/>
-    </row>
-    <row r="51" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="I50" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J50" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="K50" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="L50" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="M50" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="N50" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="O50" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="51" spans="8:15" x14ac:dyDescent="0.25">
       <c r="H51" s="2"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I51" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J51" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="K51" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="L51" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="M51" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="N51" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="O51" s="12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="52" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="H52" s="2"/>
+      <c r="I52" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="J52" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K52" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="L52" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="M52" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="N52" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="O52" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="60" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="I60" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="J60" s="18"/>
+      <c r="K60" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="L60" s="19"/>
+      <c r="M60" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="N60" s="20"/>
+      <c r="O60" s="20"/>
+    </row>
+    <row r="61" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="I61" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="J61" s="2"/>
+      <c r="K61" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="N61" s="2"/>
+    </row>
+    <row r="62" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="I62" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J62" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="N62" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="O62" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="I63" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="J63" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="L63" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="M63" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="N63" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="O63" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="64" spans="8:15" x14ac:dyDescent="0.25">
+      <c r="I64" s="21"/>
+      <c r="J64" s="22"/>
+      <c r="K64" s="22"/>
+      <c r="L64" s="22"/>
+      <c r="M64" s="22"/>
+      <c r="N64" s="22"/>
+      <c r="O64" s="22"/>
+    </row>
+    <row r="66" spans="9:15" x14ac:dyDescent="0.25">
+      <c r="I66" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="J66" s="2"/>
+      <c r="K66" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="N66" s="2"/>
+    </row>
+    <row r="67" spans="9:15" x14ac:dyDescent="0.25">
+      <c r="I67" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J67" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="N67" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="O67" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="9:15" x14ac:dyDescent="0.25">
+      <c r="I68" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="J68" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="K68" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="L68" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="M68" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="N68" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="O68" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="70" spans="9:15" x14ac:dyDescent="0.25">
+      <c r="I70" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="J70" s="2"/>
+      <c r="K70" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="N70" s="2"/>
+    </row>
+    <row r="71" spans="9:15" x14ac:dyDescent="0.25">
+      <c r="I71" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J71" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="N71" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="O71" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="9:15" x14ac:dyDescent="0.25">
+      <c r="I72" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="J72" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="K72" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="L72" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="M72" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="N72" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="O72" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -2225,7 +2968,7 @@
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -2234,7 +2977,7 @@
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -2243,7 +2986,7 @@
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -2252,7 +2995,7 @@
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -2261,7 +3004,7 @@
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
